--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75211</v>
+        <v>16.85138</v>
       </c>
       <c r="D2" t="n">
-        <v>16.74649</v>
+        <v>15.91299</v>
       </c>
       <c r="E2" t="n">
-        <v>16.91234</v>
+        <v>16.744</v>
       </c>
       <c r="F2" t="n">
-        <v>42.48357</v>
+        <v>42.6038</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04937</v>
+        <v>0.05033</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84391</v>
+        <v>1.86191</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8529</v>
+        <v>16.7995</v>
       </c>
       <c r="D3" t="n">
-        <v>16.82734</v>
+        <v>16.40312</v>
       </c>
       <c r="E3" t="n">
-        <v>16.29721</v>
+        <v>16.78279</v>
       </c>
       <c r="F3" t="n">
-        <v>42.46672</v>
+        <v>43.14264</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05136</v>
+        <v>0.05017</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84584</v>
+        <v>1.82012</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.02998</v>
+        <v>16.80324</v>
       </c>
       <c r="D4" t="n">
-        <v>16.02728</v>
+        <v>16.54908</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7056</v>
+        <v>16.70701</v>
       </c>
       <c r="F4" t="n">
-        <v>42.10463</v>
+        <v>41.72443</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05062</v>
+        <v>0.05002</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83799</v>
+        <v>1.80543</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.83406</v>
+        <v>16.78955</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8879</v>
+        <v>16.03948</v>
       </c>
       <c r="E6" t="n">
-        <v>16.30891</v>
+        <v>16.11406</v>
       </c>
       <c r="F6" t="n">
-        <v>22.10156</v>
+        <v>22.05005</v>
       </c>
       <c r="G6" t="n">
-        <v>34.82615</v>
+        <v>34.46449</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.70004</v>
+        <v>16.79967</v>
       </c>
       <c r="D7" t="n">
-        <v>16.58534</v>
+        <v>15.87671</v>
       </c>
       <c r="E7" t="n">
-        <v>16.28011</v>
+        <v>16.7365</v>
       </c>
       <c r="F7" t="n">
-        <v>21.57728</v>
+        <v>21.51343</v>
       </c>
       <c r="G7" t="n">
-        <v>34.02296</v>
+        <v>34.0771</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68179</v>
+        <v>16.51288</v>
       </c>
       <c r="D8" t="n">
-        <v>15.85089</v>
+        <v>15.50877</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2966</v>
+        <v>16.50227</v>
       </c>
       <c r="F8" t="n">
-        <v>21.59942</v>
+        <v>21.94486</v>
       </c>
       <c r="G8" t="n">
-        <v>34.95745</v>
+        <v>33.74904</v>
       </c>
     </row>
   </sheetData>
